--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDEA5D2-D68B-47A7-A208-64615770C82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B6273C-68E3-4CFE-A06F-1ACB28589914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
@@ -25482,13 +25482,13 @@
         <v>18</v>
       </c>
       <c r="H10" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="59">
         <v>46118</v>
       </c>
       <c r="J10" s="58">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -25546,13 +25546,13 @@
         <v>18</v>
       </c>
       <c r="H12" s="58">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I12" s="59">
         <v>46118</v>
       </c>
       <c r="J12" s="58">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -25642,13 +25642,13 @@
         <v>18</v>
       </c>
       <c r="H15" s="72">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I15" s="73">
         <v>46118</v>
       </c>
       <c r="J15" s="72">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -25994,10 +25994,10 @@
         <v>6</v>
       </c>
       <c r="H3" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I3" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -26023,10 +26023,10 @@
         <v>444</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -26168,10 +26168,10 @@
         <v>205</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -26284,10 +26284,10 @@
         <v>112</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I13" s="58" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -26313,10 +26313,10 @@
         <v>37</v>
       </c>
       <c r="H14" s="58" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6FCAB8-A919-42D7-83CB-A660CEA14314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D95AAEA-317F-4268-82B6-CF8B3AF67281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
@@ -25220,7 +25220,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="58">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>18</v>
@@ -25229,7 +25229,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25293,7 +25293,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25348,19 +25348,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="58">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" s="59">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J6" s="58">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -25380,19 +25380,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="58">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="58">
+        <v>3</v>
+      </c>
+      <c r="I7" s="59">
+        <v>46129</v>
+      </c>
+      <c r="J7" s="58">
         <v>5</v>
-      </c>
-      <c r="I7" s="59">
-        <v>46126</v>
-      </c>
-      <c r="J7" s="58">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -25412,19 +25412,19 @@
         <v>18</v>
       </c>
       <c r="F8" s="58">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J8" s="58">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -25444,19 +25444,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="58">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G9" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="58">
+        <v>3</v>
+      </c>
+      <c r="I9" s="59">
+        <v>46128</v>
+      </c>
+      <c r="J9" s="58">
         <v>5</v>
-      </c>
-      <c r="I9" s="59">
-        <v>46126</v>
-      </c>
-      <c r="J9" s="58">
-        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -25540,19 +25540,19 @@
         <v>18</v>
       </c>
       <c r="F12" s="58">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="58">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I12" s="59">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J12" s="58">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -25636,7 +25636,7 @@
         <v>18</v>
       </c>
       <c r="F15" s="72">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G15" s="72" t="s">
         <v>18</v>
@@ -25645,7 +25645,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="73">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J15" s="72">
         <v>3</v>
@@ -25677,7 +25677,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="75">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J16" s="74">
         <v>21</v>
@@ -25732,7 +25732,7 @@
         <v>18</v>
       </c>
       <c r="F18" s="74">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G18" s="74" t="s">
         <v>23</v>
@@ -25741,7 +25741,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="75">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J18" s="74">
         <v>21</v>
@@ -25773,7 +25773,7 @@
         <v>5</v>
       </c>
       <c r="I19" s="75">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J19" s="74">
         <v>8</v>
@@ -25802,13 +25802,13 @@
         <v>18</v>
       </c>
       <c r="H20" s="74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20" s="75">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J20" s="74">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -25894,13 +25894,13 @@
         <v>18</v>
       </c>
       <c r="H23" s="74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="75">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="J23" s="74">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -26168,10 +26168,10 @@
         <v>205</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D95AAEA-317F-4268-82B6-CF8B3AF67281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04293D9F-53FE-4950-93DC-84060E7C9241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
@@ -25220,7 +25220,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="58">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>18</v>
@@ -25229,7 +25229,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25261,7 +25261,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25293,7 +25293,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25325,7 +25325,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25348,7 +25348,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="58">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>18</v>
@@ -25357,7 +25357,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="59">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="J6" s="58">
         <v>5</v>
@@ -25380,7 +25380,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="58">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>18</v>
@@ -25389,7 +25389,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="59">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="J7" s="58">
         <v>5</v>
@@ -25412,7 +25412,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="58">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>18</v>
@@ -25421,7 +25421,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="J8" s="58">
         <v>5</v>
@@ -25453,7 +25453,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="59">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J9" s="58">
         <v>5</v>
@@ -25485,7 +25485,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J10" s="58">
         <v>4</v>
@@ -25517,7 +25517,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="59">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25549,7 +25549,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="59">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J12" s="58">
         <v>5</v>
@@ -25581,7 +25581,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25613,7 +25613,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="71">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
@@ -25636,7 +25636,7 @@
         <v>18</v>
       </c>
       <c r="F15" s="72">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G15" s="72" t="s">
         <v>18</v>
@@ -25645,7 +25645,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="73">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="J15" s="72">
         <v>3</v>
@@ -25677,7 +25677,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="75">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J16" s="74">
         <v>21</v>
@@ -25709,7 +25709,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="75">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="J17" s="74">
         <v>21</v>
@@ -25741,7 +25741,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="75">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J18" s="74">
         <v>21</v>
@@ -25764,7 +25764,7 @@
         <v>18</v>
       </c>
       <c r="F19" s="74">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" s="74" t="s">
         <v>18</v>
@@ -25773,7 +25773,7 @@
         <v>5</v>
       </c>
       <c r="I19" s="75">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J19" s="74">
         <v>8</v>
@@ -25805,7 +25805,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="75">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J20" s="74">
         <v>8</v>
@@ -25897,7 +25897,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="75">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="J23" s="74">
         <v>4</v>

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04293D9F-53FE-4950-93DC-84060E7C9241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEA4FEE-EE1B-4246-9227-D4AA8DE91728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Vendor Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master Client Data'!$A$1:$N$430</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Vendor Data'!$A$1:$Q$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Vendor Data'!$A$1:$R$255</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OLD Master Client Data'!$A$1:$L$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Siemens Vendor'!$D$1:$D$15</definedName>
   </definedNames>
@@ -13866,6 +13866,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R255" xr:uid="{9F0E62C8-53A0-4DC8-A5F1-B4C24BD3E012}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;9&amp;K000000 Internal</oddFooter>
@@ -25776,7 +25777,7 @@
         <v>46132</v>
       </c>
       <c r="J19" s="74">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -25835,10 +25836,10 @@
         <v>2</v>
       </c>
       <c r="I21" s="75">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="J21" s="74">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -25865,7 +25866,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="75">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="J22" s="74">
         <v>5</v>

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEA4FEE-EE1B-4246-9227-D4AA8DE91728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50663EE5-E3F6-43EE-914F-D93B8C0605FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Vendor Data" sheetId="1" r:id="rId1"/>
@@ -25221,7 +25221,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="58">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>18</v>
@@ -25230,7 +25230,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25262,7 +25262,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25294,7 +25294,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25326,7 +25326,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25349,7 +25349,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="58">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>18</v>
@@ -25358,7 +25358,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J6" s="58">
         <v>5</v>
@@ -25381,7 +25381,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="58">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>18</v>
@@ -25390,7 +25390,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J7" s="58">
         <v>5</v>
@@ -25413,7 +25413,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="58">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>18</v>
@@ -25422,7 +25422,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J8" s="58">
         <v>5</v>
@@ -25454,7 +25454,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J9" s="58">
         <v>5</v>
@@ -25486,7 +25486,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="J10" s="58">
         <v>4</v>
@@ -25518,7 +25518,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="59">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25550,7 +25550,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="59">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J12" s="58">
         <v>5</v>
@@ -25582,7 +25582,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25614,7 +25614,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="71">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
@@ -25646,7 +25646,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="73">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J15" s="72">
         <v>3</v>
@@ -25678,7 +25678,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="75">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J16" s="74">
         <v>21</v>
@@ -25710,7 +25710,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="75">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J17" s="74">
         <v>21</v>
@@ -25742,7 +25742,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="75">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J18" s="74">
         <v>21</v>
@@ -25765,19 +25765,19 @@
         <v>18</v>
       </c>
       <c r="F19" s="74">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G19" s="74" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="74">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I19" s="75">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J19" s="74">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -25806,7 +25806,7 @@
         <v>5</v>
       </c>
       <c r="I20" s="75">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J20" s="74">
         <v>8</v>
@@ -25836,10 +25836,10 @@
         <v>2</v>
       </c>
       <c r="I21" s="75">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="J21" s="74">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -25866,7 +25866,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="75">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="J22" s="74">
         <v>5</v>
@@ -25898,7 +25898,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="75">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="J23" s="74">
         <v>4</v>

--- a/data/lpg_stock_data.xlsx
+++ b/data/lpg_stock_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darshan.Pawar\Downloads\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50663EE5-E3F6-43EE-914F-D93B8C0605FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50DD293-92AB-40D9-85B8-62250D6B2390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{5CCA0532-4B0A-45F1-999D-D089B1DF9A89}"/>
   </bookViews>
@@ -2439,7 +2439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2639,11 +2639,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25230,7 +25227,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J2" s="58">
         <v>8</v>
@@ -25262,7 +25259,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J3" s="58">
         <v>21</v>
@@ -25294,7 +25291,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J4" s="58">
         <v>21</v>
@@ -25326,7 +25323,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J5" s="58">
         <v>21</v>
@@ -25358,7 +25355,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J6" s="58">
         <v>5</v>
@@ -25390,7 +25387,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J7" s="58">
         <v>5</v>
@@ -25422,7 +25419,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J8" s="58">
         <v>5</v>
@@ -25454,7 +25451,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J9" s="58">
         <v>5</v>
@@ -25486,10 +25483,10 @@
         <v>2</v>
       </c>
       <c r="I10" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J10" s="58">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -25518,7 +25515,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J11" s="58">
         <v>21</v>
@@ -25550,7 +25547,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J12" s="58">
         <v>5</v>
@@ -25582,7 +25579,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="59">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="J13" s="58">
         <v>21</v>
@@ -25613,294 +25610,294 @@
       <c r="H14" s="70">
         <v>5</v>
       </c>
-      <c r="I14" s="71">
-        <v>46135</v>
+      <c r="I14" s="59">
+        <v>46136</v>
       </c>
       <c r="J14" s="70">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="72">
+      <c r="A15" s="71">
         <v>53</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="72">
+      <c r="E15" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="71">
         <v>5</v>
       </c>
-      <c r="G15" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="72">
+      <c r="G15" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="71">
         <v>1</v>
       </c>
-      <c r="I15" s="73">
-        <v>46135</v>
-      </c>
-      <c r="J15" s="72">
-        <v>3</v>
+      <c r="I15" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J15" s="71">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="74">
+      <c r="A16" s="72">
         <v>4</v>
       </c>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="74">
-        <v>0</v>
-      </c>
-      <c r="G16" s="74" t="s">
+      <c r="E16" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="72">
+        <v>0</v>
+      </c>
+      <c r="G16" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="74">
+      <c r="H16" s="72">
         <v>15</v>
       </c>
-      <c r="I16" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J16" s="74">
+      <c r="I16" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J16" s="72">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="74">
-        <v>18</v>
-      </c>
-      <c r="B17" s="74" t="s">
+      <c r="A17" s="72">
+        <v>18</v>
+      </c>
+      <c r="B17" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="74" t="s">
+      <c r="E17" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="74">
-        <v>0</v>
-      </c>
-      <c r="G17" s="74" t="s">
+      <c r="F17" s="72">
+        <v>0</v>
+      </c>
+      <c r="G17" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="74">
+      <c r="H17" s="72">
         <v>15</v>
       </c>
-      <c r="I17" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J17" s="74">
+      <c r="I17" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J17" s="72">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="74">
+      <c r="A18" s="72">
         <v>5</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="74" t="s">
+      <c r="C18" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="74" t="s">
+      <c r="D18" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="74">
+      <c r="E18" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="72">
         <v>25</v>
       </c>
-      <c r="G18" s="74" t="s">
+      <c r="G18" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="74">
+      <c r="H18" s="72">
         <v>15</v>
       </c>
-      <c r="I18" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J18" s="74">
+      <c r="I18" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J18" s="72">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="74">
+      <c r="A19" s="72">
         <v>10</v>
       </c>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="74" t="s">
+      <c r="C19" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="74">
+      <c r="E19" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="72">
         <v>5</v>
       </c>
-      <c r="G19" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="74">
+      <c r="G19" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="72">
         <v>2.5</v>
       </c>
-      <c r="I19" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J19" s="74">
+      <c r="I19" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J19" s="72">
         <v>4.5</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="74">
+      <c r="A20" s="72">
         <v>55</v>
       </c>
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="74" t="s">
+      <c r="C20" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="74">
+      <c r="E20" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="72">
         <v>2</v>
       </c>
-      <c r="G20" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="74">
+      <c r="G20" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="72">
         <v>5</v>
       </c>
-      <c r="I20" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J20" s="74">
+      <c r="I20" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J20" s="72">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="74">
+      <c r="A21" s="72">
         <v>300</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="74" t="s">
+      <c r="C21" s="72" t="s">
         <v>697</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="74">
+      <c r="D21" s="72"/>
+      <c r="E21" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="72">
         <v>5</v>
       </c>
-      <c r="G21" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="74">
+      <c r="G21" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="72">
         <v>2</v>
       </c>
-      <c r="I21" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J21" s="74">
+      <c r="I21" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J21" s="72">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="74">
+      <c r="A22" s="72">
         <v>301</v>
       </c>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="74" t="s">
+      <c r="C22" s="72" t="s">
         <v>698</v>
       </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="74">
+      <c r="D22" s="72"/>
+      <c r="E22" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="72">
         <v>5</v>
       </c>
-      <c r="G22" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="74">
+      <c r="G22" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="72">
         <v>2</v>
       </c>
-      <c r="I22" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J22" s="74">
+      <c r="I22" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J22" s="72">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="74">
+      <c r="A23" s="72">
         <v>51</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="74" t="s">
+      <c r="C23" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="74" t="s">
+      <c r="D23" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="74">
+      <c r="E23" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="72">
         <v>1</v>
       </c>
-      <c r="G23" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="74">
+      <c r="G23" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="72">
         <v>2</v>
       </c>
-      <c r="I23" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J23" s="74">
+      <c r="I23" s="59">
+        <v>46136</v>
+      </c>
+      <c r="J23" s="72">
         <v>4</v>
       </c>
     </row>
